--- a/Luban/MiniTemplate/Datas/#Unit.xlsx
+++ b/Luban/MiniTemplate/Datas/#Unit.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowHeight="21260"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -86,10 +86,13 @@
     <t>战士</t>
   </si>
   <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>1_1000,2_1000,3_1,100_1000,101_1000,102_1,200_20,201_10,201_15,203_10,300_5,301_1,302_0,400_5,401_1500</t>
+  </si>
+  <si>
     <t>1001,1002,1003,1004,1005,1006,1007,1008,1009</t>
-  </si>
-  <si>
-    <t>1_1000,2_1000,3_1,100_1000,101_1000,102_1,200_20,201_10,201_15,203_10,300_5,301_1,302_0,400_5,401_1500</t>
   </si>
   <si>
     <t>远程小怪</t>
@@ -1044,16 +1047,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="3" max="3" width="17.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="16.2222222222222" customWidth="1"/>
-    <col min="5" max="5" width="49.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="17.8928571428571" customWidth="1"/>
+    <col min="4" max="4" width="16.2232142857143" customWidth="1"/>
+    <col min="5" max="5" width="49.2232142857143" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="93.3333333333333" customWidth="1"/>
-    <col min="8" max="8" width="16.8888888888889" customWidth="1"/>
-    <col min="9" max="9" width="14.3333333333333" customWidth="1"/>
-    <col min="10" max="10" width="22.5555555555556" customWidth="1"/>
+    <col min="7" max="7" width="93.3303571428571" customWidth="1"/>
+    <col min="8" max="8" width="16.8928571428571" customWidth="1"/>
+    <col min="9" max="9" width="14.3303571428571" customWidth="1"/>
+    <col min="10" max="10" width="22.5535714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1106,7 +1109,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1136,7 +1139,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" customFormat="1" spans="1:10">
+    <row r="5" customFormat="1" spans="2:10">
       <c r="B5" s="1">
         <v>1001</v>
       </c>
@@ -1160,17 +1163,22 @@
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="E6" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="2:10">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1181,7 +1189,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="2:10">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -1192,7 +1200,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="2:10">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -1203,7 +1211,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="2:10">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -1214,7 +1222,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="2:10">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -1225,7 +1233,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="2:10">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -1236,7 +1244,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="2:10">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -1247,7 +1255,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="2:10">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -1258,7 +1266,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="2:10">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -1269,15 +1277,15 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="2:10">
       <c r="B16" s="1">
         <v>2001</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" s="1">
         <v>7001</v>
@@ -1334,74 +1342,72 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:7">
       <c r="B21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:7">
       <c r="B22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:7">
       <c r="B23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:7">
       <c r="B24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:7">
       <c r="B26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:7">
       <c r="B28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:7">
       <c r="B29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:7">
       <c r="B30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:7">
       <c r="B31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:7">
       <c r="B32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="5:6">
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
     </row>
     <row r="40" customFormat="1" spans="2:7">
       <c r="B40" s="1"/>
-      <c r="C40"/>
-      <c r="D40"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
